--- a/Risk.xlsx
+++ b/Risk.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Documents\AI\Risk\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E416DCD3-4328-48BF-90CD-4B6B9CAA7D68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBBA76CD-C7A9-4C61-975D-B08D0C2987AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="10200" tabRatio="500" firstSheet="16" activeTab="18" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,11 +27,11 @@
     <sheet name="Risk 9.0 Intrest Rate" sheetId="25" r:id="rId12"/>
     <sheet name="Risk 10.0 EDA" sheetId="14" r:id="rId13"/>
     <sheet name="Risk 11.0 Bureau" sheetId="19" r:id="rId14"/>
-    <sheet name="Risk 12.0 Applications" sheetId="20" r:id="rId15"/>
+    <sheet name="Risk 12.0 Previous" sheetId="20" r:id="rId15"/>
     <sheet name="Risk 13.0 Installments" sheetId="21" r:id="rId16"/>
     <sheet name="Risk 14.0 Balance" sheetId="24" r:id="rId17"/>
     <sheet name="Risk 15.0.0 PCA" sheetId="26" r:id="rId18"/>
-    <sheet name="Risk 16.0.0 Modeling" sheetId="28" r:id="rId19"/>
+    <sheet name="Risk 16.0.0 Train" sheetId="28" r:id="rId19"/>
     <sheet name="Alert" sheetId="4" state="hidden" r:id="rId20"/>
   </sheets>
   <definedNames>
@@ -67,7 +67,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="233">
   <si>
     <t>Version</t>
   </si>
@@ -2660,6 +2660,18 @@
   <si>
     <t>Risk 15.0.0</t>
   </si>
+  <si>
+    <t>Risk 5.0.1</t>
+  </si>
+  <si>
+    <t>Eliminated Polynomial features</t>
+  </si>
+  <si>
+    <t>kept domain knowledge features.</t>
+  </si>
+  <si>
+    <t>Eliminated Feature Engine Library, drop collinear features.</t>
+  </si>
 </sst>
 </file>
 
@@ -34934,7 +34946,9 @@
       <c r="C2" s="4" t="s">
         <v>226</v>
       </c>
-      <c r="D2" s="3"/>
+      <c r="D2" s="3" t="s">
+        <v>232</v>
+      </c>
       <c r="G2" s="5"/>
     </row>
     <row r="3" spans="1:9">
@@ -59602,17 +59616,27 @@
       <c r="I4" s="5"/>
     </row>
     <row r="5" spans="1:9">
-      <c r="A5" s="3"/>
-      <c r="B5" s="4"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="3"/>
+      <c r="A5" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>230</v>
+      </c>
       <c r="G5" s="5"/>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="3"/>
       <c r="B6" s="6"/>
       <c r="C6" s="7"/>
-      <c r="D6" s="3"/>
+      <c r="D6" s="3" t="s">
+        <v>231</v>
+      </c>
       <c r="G6" s="5"/>
     </row>
     <row r="7" spans="1:9">
